--- a/assets/downloads/2.4_Collaboration_Improvement_Workbook_QGov.xlsx
+++ b/assets/downloads/2.4_Collaboration_Improvement_Workbook_QGov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpwqld.sharepoint.com/sites/CDSDCT/Shared Documents/Digital Capability Framework POW/3. AP Delivery/2.0 Digital Literacy/06 Project Documentation/Build/GitHub Downloadable Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A7CAA3C09C84E15E26F933C23013218D35FE8CB2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74842305-1C21-455A-94AF-6FEBA4EA56C1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_A7CAA3C09C84E15E26F933C23013218D35FE8CB2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1A4EFC0-8205-4117-A69B-C8C0519A97AA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,7 +223,7 @@
       <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,17 +242,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE5F1F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF005EA8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3F8FB"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -277,36 +273,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -625,22 +624,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
@@ -650,22 +649,22 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="52" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="39" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1"/>
@@ -679,22 +678,22 @@
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -704,22 +703,22 @@
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
@@ -729,49 +728,49 @@
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
@@ -781,134 +780,134 @@
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
+      <c r="A21" s="8">
         <v>1</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="9"/>
+      <c r="D21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
+      <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="9"/>
+      <c r="D22" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
+      <c r="A23" s="8">
         <v>3</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
+      <c r="A24" s="8">
         <v>4</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="9"/>
+      <c r="D24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
+      <c r="A25" s="8">
         <v>5</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="9"/>
+      <c r="D25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
+      <c r="A26" s="8">
         <v>6</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
+      <c r="A27" s="8">
         <v>7</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="9"/>
+      <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
+      <c r="A28" s="8">
         <v>8</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
@@ -918,40 +917,40 @@
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
@@ -961,31 +960,31 @@
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
@@ -995,43 +994,43 @@
       <c r="E38" s="1"/>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="1" t="s">
         <v>39</v>
       </c>
@@ -1044,44 +1043,63 @@
       <c r="E43" s="1"/>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A20:E28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="35">
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A41:D41"/>
@@ -1098,25 +1116,6 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A45:B45"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape"/>
@@ -1138,15 +1137,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010066AE4C6A13B8E141A8E674DFA32CA6F2" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5761630454da6c2d94458fc443ef2e29">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="25084aa5-12fd-4011-b528-cc6f0e62d12b" xmlns:ns3="3d81d758-da71-42ef-a10b-ca28e43b4f75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7e2faffedb6149b0744f7bb7ad460f5" ns2:_="" ns3:_="">
     <xsd:import namespace="25084aa5-12fd-4011-b528-cc6f0e62d12b"/>
@@ -1381,6 +1371,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82DFB394-070D-44B9-8C38-55B13CA57204}">
   <ds:schemaRefs>
@@ -1393,14 +1392,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E059D0A5-FB15-4AC9-A1D9-63EF8FA313FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD01A92-D40D-4BF7-9E77-5D8FF332F037}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1417,4 +1408,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E059D0A5-FB15-4AC9-A1D9-63EF8FA313FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>